--- a/组合实盘追踪/20260602_银河.xlsx
+++ b/组合实盘追踪/20260602_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>671.6</v>
+        <v>675</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.2</v>
+        <v>3.2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0003</v>
+        <v>0.0048</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-39.5</v>
+        <v>-36.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0555</v>
+        <v>-0.0508</v>
       </c>
       <c r="L2" s="1">
-        <v>-39.5</v>
+        <v>-36.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0555</v>
+        <v>-0.0508</v>
       </c>
       <c r="N2" s="1">
-        <v>-25.6</v>
+        <v>-22.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-25.6</v>
+        <v>-22.4</v>
       </c>
       <c r="P2" s="1">
-        <v>-39.5</v>
+        <v>-36.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.023</v>
+        <v>0.0231</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>17</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0003</v>
+        <v>0.0048</v>
       </c>
       <c r="U2" s="5">
-        <v>3.358</v>
+        <v>3.375</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.059</v>
+        <v>0.0536</v>
       </c>
       <c r="X2" s="2">
-        <v>-0.0012</v>
+        <v>0.0039</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0213</v>
+        <v>-0.0163</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1382</v>
+        <v>0.1439</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4031</v>
+        <v>0.4102</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>826.8</v>
+        <v>816</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.4</v>
+        <v>-13.2</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0159</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-36.1</v>
+        <v>-46.9</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0418</v>
+        <v>-0.0544</v>
       </c>
       <c r="L3" s="1">
-        <v>-36.1</v>
+        <v>-46.9</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0418</v>
+        <v>-0.0544</v>
       </c>
       <c r="N3" s="1">
-        <v>-11.2</v>
+        <v>-22.4</v>
       </c>
       <c r="O3" s="1">
-        <v>-11.2</v>
+        <v>-23.2</v>
       </c>
       <c r="P3" s="1">
-        <v>-36.1</v>
+        <v>-48.1</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0284</v>
+        <v>0.0279</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>17</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0159</v>
       </c>
       <c r="U3" s="5">
-        <v>2.067</v>
+        <v>2.04</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0435</v>
+        <v>0.0574</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.044</v>
+        <v>-0.0565</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0248</v>
+        <v>0.0114</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0477</v>
+        <v>0.034</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0732</v>
+        <v>0.0592</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>712.8</v>
+        <v>738.1</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-24.3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.033</v>
+        <v>0.0014</v>
       </c>
       <c r="L4" s="1">
-        <v>-24.3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.033</v>
+        <v>0.0014</v>
       </c>
       <c r="N4" s="1">
-        <v>6.6</v>
+        <v>31.9</v>
       </c>
       <c r="O4" s="1">
-        <v>7.7</v>
+        <v>30.8</v>
       </c>
       <c r="P4" s="1">
-        <v>-23.2</v>
+        <v>-0.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0245</v>
+        <v>0.0252</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>17</v>
       </c>
       <c r="T4" s="2">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="U4" s="5">
-        <v>0.648</v>
+        <v>0.671</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.034</v>
+        <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0047</v>
+        <v>0.0404</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.054</v>
+        <v>-0.0204</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.166</v>
+        <v>-0.1364</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0912</v>
+        <v>-0.0589</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>973.4</v>
+        <v>987.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.2</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0002</v>
+        <v>0.0144</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-17.9</v>
+        <v>-3.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0181</v>
+        <v>-0.0037</v>
       </c>
       <c r="L5" s="1">
-        <v>-17.9</v>
+        <v>-3.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0181</v>
+        <v>-0.0037</v>
       </c>
       <c r="N5" s="1">
-        <v>-17.6</v>
+        <v>-3.6</v>
       </c>
       <c r="O5" s="1">
-        <v>-17.6</v>
+        <v>-3.6</v>
       </c>
       <c r="P5" s="1">
-        <v>-17.9</v>
+        <v>-3.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0334</v>
+        <v>0.0337</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>17</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0002</v>
+        <v>0.0144</v>
       </c>
       <c r="U5" s="5">
-        <v>4.867</v>
+        <v>4.938</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0185</v>
+        <v>0.0038</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0089</v>
+        <v>0.0236</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0301</v>
+        <v>0.0451</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0654</v>
+        <v>0.0809</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2897</v>
+        <v>0.3085</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>930</v>
+        <v>940.7</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.4</v>
+        <v>6.3</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0047</v>
+        <v>0.0067</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-43.7</v>
+        <v>-33</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0449</v>
+        <v>-0.0339</v>
       </c>
       <c r="L6" s="1">
-        <v>-43.7</v>
+        <v>-33</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0449</v>
+        <v>-0.0339</v>
       </c>
       <c r="N6" s="1">
-        <v>-6.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" s="1">
-        <v>-6.3</v>
+        <v>4.2</v>
       </c>
       <c r="P6" s="1">
-        <v>-43.7</v>
+        <v>-33.2</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0319</v>
+        <v>0.0321</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>17</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0047</v>
+        <v>0.0067</v>
       </c>
       <c r="U6" s="5">
-        <v>9.3</v>
+        <v>9.407</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.047</v>
+        <v>0.0351</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.039</v>
+        <v>-0.028</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1493</v>
+        <v>-0.1395</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0152</v>
+        <v>0.0269</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.262</v>
+        <v>0.2765</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3032.1</v>
+        <v>3034.8</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>13.35</v>
+        <v>16.05</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0044</v>
+        <v>0.0053</v>
       </c>
       <c r="L7" s="1">
-        <v>13.35</v>
+        <v>16.05</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0044</v>
+        <v>0.0053</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7" s="1">
-        <v>13.35</v>
+        <v>16.05</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.104</v>
+        <v>0.1037</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>17</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.123</v>
+        <v>1.124</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0054</v>
+        <v>0.0063</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0135</v>
+        <v>0.0144</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0154</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0234</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>796.6</v>
+        <v>814.4</v>
       </c>
       <c r="D8" s="1">
-        <v>3.8</v>
+        <v>21.6</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0048</v>
+        <v>0.0272</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>9.9</v>
+        <v>27.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0126</v>
+        <v>0.0352</v>
       </c>
       <c r="L8" s="1">
-        <v>9.9</v>
+        <v>27.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0126</v>
+        <v>0.0352</v>
       </c>
       <c r="N8" s="1">
-        <v>-35.8</v>
+        <v>-18.2</v>
       </c>
       <c r="O8" s="1">
-        <v>-35.8</v>
+        <v>-18.4</v>
       </c>
       <c r="P8" s="1">
-        <v>9.9</v>
+        <v>27.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0273</v>
+        <v>0.0278</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>17</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0048</v>
+        <v>0.0272</v>
       </c>
       <c r="U8" s="5">
-        <v>3.983</v>
+        <v>4.072</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0797</v>
+        <v>0.1038</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2066</v>
+        <v>0.2335</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2961</v>
+        <v>0.325</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0197</v>
+        <v>1.0649</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19681.2</v>
+        <v>19742.8</v>
       </c>
       <c r="D9" s="1">
-        <v>29.4</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0015</v>
+        <v>0.0046</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-696.44</v>
+        <v>-634.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0342</v>
+        <v>-0.0312</v>
       </c>
       <c r="L9" s="1">
-        <v>-696.44</v>
+        <v>-634.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0342</v>
+        <v>-0.0312</v>
       </c>
       <c r="N9" s="1">
-        <v>-120.4</v>
+        <v>-58.8</v>
       </c>
       <c r="O9" s="1">
-        <v>-117.6</v>
+        <v>-60.2</v>
       </c>
       <c r="P9" s="1">
-        <v>-693.64</v>
+        <v>-636.24</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6753</v>
+        <v>0.6744</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>17</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0015</v>
+        <v>0.0046</v>
       </c>
       <c r="U9" s="5">
-        <v>14.058</v>
+        <v>14.102</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0354</v>
+        <v>0.0321</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0164</v>
+        <v>-0.0134</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0369</v>
+        <v>-0.0338</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0491</v>
+        <v>0.0524</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1702</v>
+        <v>0.1739</v>
       </c>
     </row>
     <row r="10">
@@ -1229,16 +1229,16 @@
         <v>-0.0329</v>
       </c>
       <c r="N10" s="1">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="O10" s="1">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="P10" s="1">
-        <v>-22.1</v>
+        <v>-22.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0223</v>
+        <v>0.0222</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D11" s="1">
-        <v>12.4</v>
+        <v>16.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0144</v>
+        <v>0.0191</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,19 +1300,19 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0134</v>
+        <v>0.018</v>
       </c>
       <c r="L11" s="1">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0134</v>
+        <v>0.018</v>
       </c>
       <c r="N11" s="1">
-        <v>8.4</v>
+        <v>13.2</v>
       </c>
       <c r="O11" s="1">
         <v>13.2</v>
@@ -1330,10 +1330,10 @@
         <v>17</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0144</v>
+        <v>0.0191</v>
       </c>
       <c r="U11" s="5">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0456</v>
+        <v>0.0504</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0069</v>
+        <v>0.0115</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.179</v>
+        <v>0.1844</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3148</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29146.5</v>
+        <v>29275.4</v>
       </c>
       <c r="D12" s="1">
-        <v>41.2</v>
+        <v>170.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0014</v>
+        <v>0.0058</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-845.29</v>
+        <v>-716.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0282</v>
+        <v>-0.0239</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-187.1</v>
+        <v>-58.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-178.4</v>
+        <v>-62.5</v>
       </c>
       <c r="P12" s="1">
-        <v>-836.99</v>
+        <v>-721.09</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>
